--- a/Gibsons/Gibson_WEST_POSITION_LIST_All_Emails.xlsx
+++ b/Gibsons/Gibson_WEST_POSITION_LIST_All_Emails.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="126">
   <si>
     <t>Vessel</t>
   </si>
@@ -389,9 +389,6 @@
   </si>
   <si>
     <t>Gibson</t>
-  </si>
-  <si>
-    <t>2026-02-27 16:01:30</t>
   </si>
   <si>
     <t>C:\Users\THADLOW\OneDrive - Axpo Services AG\Desktop\SHIPPING BROKER REPORTS\Gibsons\Emails\2026-02-27_160134__FW_ Gibson VLGC update\2026-02-27_160134__FW_ Gibson VLGC update.msg</t>
@@ -859,10 +856,10 @@
         <v>124</v>
       </c>
       <c r="P2" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q2" t="s">
         <v>125</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -912,10 +909,10 @@
         <v>124</v>
       </c>
       <c r="P3" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q3" t="s">
         <v>125</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -965,10 +962,10 @@
         <v>124</v>
       </c>
       <c r="P4" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q4" t="s">
         <v>125</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -1018,10 +1015,10 @@
         <v>124</v>
       </c>
       <c r="P5" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q5" t="s">
         <v>125</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -1071,10 +1068,10 @@
         <v>124</v>
       </c>
       <c r="P6" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q6" t="s">
         <v>125</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -1124,10 +1121,10 @@
         <v>124</v>
       </c>
       <c r="P7" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q7" t="s">
         <v>125</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -1177,10 +1174,10 @@
         <v>124</v>
       </c>
       <c r="P8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q8" t="s">
         <v>125</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -1230,10 +1227,10 @@
         <v>124</v>
       </c>
       <c r="P9" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q9" t="s">
         <v>125</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -1283,10 +1280,10 @@
         <v>124</v>
       </c>
       <c r="P10" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q10" t="s">
         <v>125</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -1336,10 +1333,10 @@
         <v>124</v>
       </c>
       <c r="P11" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q11" t="s">
         <v>125</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -1389,10 +1386,10 @@
         <v>124</v>
       </c>
       <c r="P12" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q12" t="s">
         <v>125</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -1442,10 +1439,10 @@
         <v>124</v>
       </c>
       <c r="P13" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q13" t="s">
         <v>125</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -1495,10 +1492,10 @@
         <v>124</v>
       </c>
       <c r="P14" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q14" t="s">
         <v>125</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -1548,10 +1545,10 @@
         <v>124</v>
       </c>
       <c r="P15" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q15" t="s">
         <v>125</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -1601,10 +1598,10 @@
         <v>124</v>
       </c>
       <c r="P16" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q16" t="s">
         <v>125</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>126</v>
       </c>
     </row>
   </sheetData>
